--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -27638,11 +27638,7 @@
       </c>
       <c r="E11" s="23" t="n"/>
       <c r="F11" s="23" t="n"/>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="G11" s="21" t="n"/>
       <c r="H11" s="21" t="n"/>
       <c r="I11" s="24" t="inlineStr">
         <is>

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3622,11 +3622,7 @@
         </is>
       </c>
       <c r="D15" s="23" t="n"/>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="24" t="n"/>
       <c r="G15" s="24" t="n"/>
       <c r="H15" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3446,11 +3446,7 @@
         </is>
       </c>
       <c r="D9" s="23" t="n"/>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E9" s="21" t="n"/>
       <c r="F9" s="24" t="n"/>
       <c r="G9" s="24" t="n"/>
       <c r="H9" t="inlineStr">
@@ -3622,7 +3618,11 @@
         </is>
       </c>
       <c r="D15" s="23" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F15" s="24" t="n"/>
       <c r="G15" s="24" t="n"/>
       <c r="H15" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3446,7 +3446,11 @@
         </is>
       </c>
       <c r="D9" s="23" t="n"/>
-      <c r="E9" s="21" t="n"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F9" s="24" t="n"/>
       <c r="G9" s="24" t="n"/>
       <c r="H9" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -29582,7 +29582,11 @@
           <t>en euros</t>
         </is>
       </c>
-      <c r="G63" s="21" t="n"/>
+      <c r="G63" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="H63" s="21" t="n"/>
       <c r="I63" s="24" t="inlineStr">
         <is>
@@ -29623,7 +29627,11 @@
           <t>en euros</t>
         </is>
       </c>
-      <c r="G64" s="21" t="n"/>
+      <c r="G64" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="H64" s="21" t="n"/>
       <c r="I64" s="24" t="inlineStr">
         <is>

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3386,11 +3386,7 @@
         </is>
       </c>
       <c r="D7" s="23" t="n"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="E7" s="21" t="n"/>
       <c r="F7" s="24" t="n"/>
       <c r="G7" s="24" t="n"/>
       <c r="H7" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3386,7 +3386,11 @@
         </is>
       </c>
       <c r="D7" s="23" t="n"/>
-      <c r="E7" s="21" t="n"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F7" s="24" t="n"/>
       <c r="G7" s="24" t="n"/>
       <c r="H7" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -3622,7 +3622,11 @@
         </is>
       </c>
       <c r="D15" s="23" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F15" s="24" t="n"/>
       <c r="G15" s="24" t="n"/>
       <c r="H15" t="inlineStr">

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -18462,7 +18462,11 @@
         </is>
       </c>
       <c r="E107" s="23" t="n"/>
-      <c r="F107" s="21" t="n"/>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="G107" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -11408,7 +11408,11 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="H91" s="21" t="n"/>
+      <c r="H91" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="I91" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>
@@ -11588,11 +11592,7 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="H95" s="21" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
+      <c r="H95" s="21" t="n"/>
       <c r="I95" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>

--- a/configuration.xlsx
+++ b/configuration.xlsx
@@ -32739,7 +32739,11 @@
           <t>@NASA</t>
         </is>
       </c>
-      <c r="E25" s="21" t="n"/>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>
@@ -32807,7 +32811,11 @@
           <t>@EuropeanSpaceAgency</t>
         </is>
       </c>
-      <c r="E27" s="21" t="n"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>
@@ -32935,7 +32943,11 @@
           <t>@NotaBeneMovies</t>
         </is>
       </c>
-      <c r="E31" s="21" t="n"/>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>
@@ -32969,7 +32981,11 @@
           <t>@LeDessousDesCartes</t>
         </is>
       </c>
-      <c r="E32" s="21" t="n"/>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
           <t>à vérifier</t>
